--- a/diseases/d123/2005-2009.xlsx
+++ b/diseases/d123/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.03812368925990863</v>
       </c>
@@ -1309,9 +1306,6 @@
       <c r="O5" t="n">
         <v>0</v>
       </c>
-      <c r="Q5" t="n">
-        <v>0</v>
-      </c>
       <c r="R5" t="n">
         <v>0</v>
       </c>
@@ -1705,9 +1699,6 @@
       <c r="O7" t="n">
         <v>2</v>
       </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
       <c r="R7" t="n">
         <v>0.04326079075534206</v>
       </c>
@@ -2249,9 +2240,6 @@
       <c r="O10" t="n">
         <v>1</v>
       </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
       <c r="R10" t="n">
         <v>0.01906184462995432</v>
       </c>
@@ -2645,9 +2633,6 @@
       <c r="O12" t="n">
         <v>2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.04326079075534206</v>
       </c>
@@ -3189,9 +3174,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3585,9 +3567,6 @@
       <c r="O17" t="n">
         <v>2</v>
       </c>
-      <c r="Q17" t="n">
-        <v>0</v>
-      </c>
       <c r="R17" t="n">
         <v>0.04326079075534206</v>
       </c>
@@ -4129,9 +4108,6 @@
       <c r="O20" t="n">
         <v>0</v>
       </c>
-      <c r="Q20" t="n">
-        <v>0</v>
-      </c>
       <c r="R20" t="n">
         <v>0</v>
       </c>
@@ -4525,9 +4501,6 @@
       <c r="O22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
-      </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
@@ -5069,9 +5042,6 @@
       <c r="O25" t="n">
         <v>0</v>
       </c>
-      <c r="Q25" t="n">
-        <v>0</v>
-      </c>
       <c r="R25" t="n">
         <v>0</v>
       </c>
@@ -5465,9 +5435,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -6009,9 +5976,6 @@
       <c r="O30" t="n">
         <v>0</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0</v>
       </c>
@@ -6405,9 +6369,6 @@
       <c r="O32" t="n">
         <v>0</v>
       </c>
-      <c r="Q32" t="n">
-        <v>0</v>
-      </c>
       <c r="R32" t="n">
         <v>0</v>
       </c>
@@ -6949,9 +6910,6 @@
       <c r="O35" t="n">
         <v>5</v>
       </c>
-      <c r="Q35" t="n">
-        <v>0</v>
-      </c>
       <c r="R35" t="n">
         <v>0.09530922314977158</v>
       </c>
@@ -7345,9 +7303,6 @@
       <c r="O37" t="n">
         <v>0</v>
       </c>
-      <c r="Q37" t="n">
-        <v>0</v>
-      </c>
       <c r="R37" t="n">
         <v>0</v>
       </c>
@@ -7889,9 +7844,6 @@
       <c r="O40" t="n">
         <v>9</v>
       </c>
-      <c r="Q40" t="n">
-        <v>0</v>
-      </c>
       <c r="R40" t="n">
         <v>0.1715566016695889</v>
       </c>
@@ -8285,9 +8237,6 @@
       <c r="O42" t="n">
         <v>0</v>
       </c>
-      <c r="Q42" t="n">
-        <v>0</v>
-      </c>
       <c r="R42" t="n">
         <v>0</v>
       </c>
@@ -8829,9 +8778,6 @@
       <c r="O45" t="n">
         <v>17</v>
       </c>
-      <c r="Q45" t="n">
-        <v>0</v>
-      </c>
       <c r="R45" t="n">
         <v>0.3240513587092234</v>
       </c>
@@ -9225,9 +9171,6 @@
       <c r="O47" t="n">
         <v>4</v>
       </c>
-      <c r="Q47" t="n">
-        <v>0</v>
-      </c>
       <c r="R47" t="n">
         <v>0.08652158151068412</v>
       </c>
@@ -9769,9 +9712,6 @@
       <c r="O50" t="n">
         <v>15</v>
       </c>
-      <c r="Q50" t="n">
-        <v>0</v>
-      </c>
       <c r="R50" t="n">
         <v>0.2859276694493147</v>
       </c>
@@ -10165,9 +10105,6 @@
       <c r="O52" t="n">
         <v>4</v>
       </c>
-      <c r="Q52" t="n">
-        <v>0</v>
-      </c>
       <c r="R52" t="n">
         <v>0.08652158151068412</v>
       </c>
@@ -10709,9 +10646,6 @@
       <c r="O55" t="n">
         <v>10</v>
       </c>
-      <c r="Q55" t="n">
-        <v>0</v>
-      </c>
       <c r="R55" t="n">
         <v>0.1906184462995432</v>
       </c>
@@ -11105,9 +11039,6 @@
       <c r="O57" t="n">
         <v>2</v>
       </c>
-      <c r="Q57" t="n">
-        <v>0</v>
-      </c>
       <c r="R57" t="n">
         <v>0.04326079075534206</v>
       </c>
@@ -11649,9 +11580,6 @@
       <c r="O60" t="n">
         <v>3</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0.05718553388986295</v>
       </c>
@@ -12045,9 +11973,6 @@
       <c r="O62" t="n">
         <v>1</v>
       </c>
-      <c r="Q62" t="n">
-        <v>0</v>
-      </c>
       <c r="R62" t="n">
         <v>0.02163039537767103</v>
       </c>
@@ -12589,9 +12514,6 @@
       <c r="O65" t="n">
         <v>0</v>
       </c>
-      <c r="Q65" t="n">
-        <v>0</v>
-      </c>
       <c r="R65" t="n">
         <v>0</v>
       </c>
@@ -12985,9 +12907,6 @@
       <c r="O67" t="n">
         <v>0</v>
       </c>
-      <c r="Q67" t="n">
-        <v>0</v>
-      </c>
       <c r="R67" t="n">
         <v>0</v>
       </c>
@@ -13381,9 +13300,6 @@
       <c r="O69" t="n">
         <v>0</v>
       </c>
-      <c r="Q69" t="n">
-        <v>0</v>
-      </c>
       <c r="R69" t="n">
         <v>0</v>
       </c>
@@ -13529,9 +13445,6 @@
       <c r="O70" t="n">
         <v>4</v>
       </c>
-      <c r="Q70" t="n">
-        <v>0</v>
-      </c>
       <c r="R70" t="n">
         <v>0.08582781138651825</v>
       </c>
@@ -14073,9 +13986,6 @@
       <c r="O73" t="n">
         <v>1</v>
       </c>
-      <c r="Q73" t="n">
-        <v>0</v>
-      </c>
       <c r="R73" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -14469,9 +14379,6 @@
       <c r="O75" t="n">
         <v>0</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0</v>
       </c>
@@ -14617,9 +14524,6 @@
       <c r="O76" t="n">
         <v>0</v>
       </c>
-      <c r="Q76" t="n">
-        <v>0</v>
-      </c>
       <c r="R76" t="n">
         <v>0</v>
       </c>
@@ -15161,9 +15065,6 @@
       <c r="O79" t="n">
         <v>2</v>
       </c>
-      <c r="Q79" t="n">
-        <v>0</v>
-      </c>
       <c r="R79" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -15557,9 +15458,6 @@
       <c r="O81" t="n">
         <v>0</v>
       </c>
-      <c r="Q81" t="n">
-        <v>0</v>
-      </c>
       <c r="R81" t="n">
         <v>0</v>
       </c>
@@ -15705,9 +15603,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -16249,9 +16144,6 @@
       <c r="O85" t="n">
         <v>5</v>
       </c>
-      <c r="Q85" t="n">
-        <v>0</v>
-      </c>
       <c r="R85" t="n">
         <v>0.09494428337146771</v>
       </c>
@@ -16645,9 +16537,6 @@
       <c r="O87" t="n">
         <v>0</v>
       </c>
-      <c r="Q87" t="n">
-        <v>0</v>
-      </c>
       <c r="R87" t="n">
         <v>0</v>
       </c>
@@ -16793,9 +16682,6 @@
       <c r="O88" t="n">
         <v>0</v>
       </c>
-      <c r="Q88" t="n">
-        <v>0</v>
-      </c>
       <c r="R88" t="n">
         <v>0</v>
       </c>
@@ -17337,9 +17223,6 @@
       <c r="O91" t="n">
         <v>2</v>
       </c>
-      <c r="Q91" t="n">
-        <v>0</v>
-      </c>
       <c r="R91" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -17733,9 +17616,6 @@
       <c r="O93" t="n">
         <v>0</v>
       </c>
-      <c r="Q93" t="n">
-        <v>0</v>
-      </c>
       <c r="R93" t="n">
         <v>0</v>
       </c>
@@ -17881,9 +17761,6 @@
       <c r="O94" t="n">
         <v>1</v>
       </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
       <c r="R94" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -18425,9 +18302,6 @@
       <c r="O97" t="n">
         <v>4</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0.07595542669717416</v>
       </c>
@@ -18821,9 +18695,6 @@
       <c r="O99" t="n">
         <v>0</v>
       </c>
-      <c r="Q99" t="n">
-        <v>0</v>
-      </c>
       <c r="R99" t="n">
         <v>0</v>
       </c>
@@ -18969,9 +18840,6 @@
       <c r="O100" t="n">
         <v>0</v>
       </c>
-      <c r="Q100" t="n">
-        <v>0</v>
-      </c>
       <c r="R100" t="n">
         <v>0</v>
       </c>
@@ -19513,9 +19381,6 @@
       <c r="O103" t="n">
         <v>59</v>
       </c>
-      <c r="Q103" t="n">
-        <v>0</v>
-      </c>
       <c r="R103" t="n">
         <v>1.120342543783319</v>
       </c>
@@ -19909,9 +19774,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -20057,9 +19919,6 @@
       <c r="O106" t="n">
         <v>0</v>
       </c>
-      <c r="Q106" t="n">
-        <v>0</v>
-      </c>
       <c r="R106" t="n">
         <v>0</v>
       </c>
@@ -20601,9 +20460,6 @@
       <c r="O109" t="n">
         <v>217</v>
       </c>
-      <c r="Q109" t="n">
-        <v>0</v>
-      </c>
       <c r="R109" t="n">
         <v>4.120581898321698</v>
       </c>
@@ -20997,9 +20853,6 @@
       <c r="O111" t="n">
         <v>0</v>
       </c>
-      <c r="Q111" t="n">
-        <v>0</v>
-      </c>
       <c r="R111" t="n">
         <v>0</v>
       </c>
@@ -21145,9 +20998,6 @@
       <c r="O112" t="n">
         <v>1</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -21689,9 +21539,6 @@
       <c r="O115" t="n">
         <v>142</v>
       </c>
-      <c r="Q115" t="n">
-        <v>0</v>
-      </c>
       <c r="R115" t="n">
         <v>2.696417647749683</v>
       </c>
@@ -22085,9 +21932,6 @@
       <c r="O117" t="n">
         <v>0</v>
       </c>
-      <c r="Q117" t="n">
-        <v>0</v>
-      </c>
       <c r="R117" t="n">
         <v>0</v>
       </c>
@@ -22233,9 +22077,6 @@
       <c r="O118" t="n">
         <v>3</v>
       </c>
-      <c r="Q118" t="n">
-        <v>0</v>
-      </c>
       <c r="R118" t="n">
         <v>0.06437085853988869</v>
       </c>
@@ -22777,9 +22618,6 @@
       <c r="O121" t="n">
         <v>38</v>
       </c>
-      <c r="Q121" t="n">
-        <v>0</v>
-      </c>
       <c r="R121" t="n">
         <v>0.7215765536231545</v>
       </c>
@@ -23173,9 +23011,6 @@
       <c r="O123" t="n">
         <v>0</v>
       </c>
-      <c r="Q123" t="n">
-        <v>0</v>
-      </c>
       <c r="R123" t="n">
         <v>0</v>
       </c>
@@ -23321,9 +23156,6 @@
       <c r="O124" t="n">
         <v>1</v>
       </c>
-      <c r="Q124" t="n">
-        <v>0</v>
-      </c>
       <c r="R124" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -23865,9 +23697,6 @@
       <c r="O127" t="n">
         <v>2</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -24261,9 +24090,6 @@
       <c r="O129" t="n">
         <v>0</v>
       </c>
-      <c r="Q129" t="n">
-        <v>0</v>
-      </c>
       <c r="R129" t="n">
         <v>0</v>
       </c>
@@ -24409,9 +24235,6 @@
       <c r="O130" t="n">
         <v>1</v>
       </c>
-      <c r="Q130" t="n">
-        <v>0</v>
-      </c>
       <c r="R130" t="n">
         <v>0.02145695284662956</v>
       </c>
@@ -24953,9 +24776,6 @@
       <c r="O133" t="n">
         <v>3</v>
       </c>
-      <c r="Q133" t="n">
-        <v>0</v>
-      </c>
       <c r="R133" t="n">
         <v>0.05696657002288063</v>
       </c>
@@ -25349,9 +25169,6 @@
       <c r="O135" t="n">
         <v>0</v>
       </c>
-      <c r="Q135" t="n">
-        <v>0</v>
-      </c>
       <c r="R135" t="n">
         <v>0</v>
       </c>
@@ -25497,9 +25314,6 @@
       <c r="O136" t="n">
         <v>2</v>
       </c>
-      <c r="Q136" t="n">
-        <v>0</v>
-      </c>
       <c r="R136" t="n">
         <v>0.04291390569325913</v>
       </c>
@@ -26041,9 +25855,6 @@
       <c r="O139" t="n">
         <v>1</v>
       </c>
-      <c r="Q139" t="n">
-        <v>0</v>
-      </c>
       <c r="R139" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -26437,9 +26248,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -26833,9 +26641,6 @@
       <c r="O143" t="n">
         <v>0</v>
       </c>
-      <c r="Q143" t="n">
-        <v>0</v>
-      </c>
       <c r="R143" t="n">
         <v>0</v>
       </c>
@@ -26981,9 +26786,6 @@
       <c r="O144" t="n">
         <v>4</v>
       </c>
-      <c r="Q144" t="n">
-        <v>0</v>
-      </c>
       <c r="R144" t="n">
         <v>0.08494354439680528</v>
       </c>
@@ -27525,9 +27327,6 @@
       <c r="O147" t="n">
         <v>1</v>
       </c>
-      <c r="Q147" t="n">
-        <v>0</v>
-      </c>
       <c r="R147" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -27921,9 +27720,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -28069,9 +27865,6 @@
       <c r="O150" t="n">
         <v>2</v>
       </c>
-      <c r="Q150" t="n">
-        <v>0</v>
-      </c>
       <c r="R150" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -28613,9 +28406,6 @@
       <c r="O153" t="n">
         <v>2</v>
       </c>
-      <c r="Q153" t="n">
-        <v>0</v>
-      </c>
       <c r="R153" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -29009,9 +28799,6 @@
       <c r="O155" t="n">
         <v>0</v>
       </c>
-      <c r="Q155" t="n">
-        <v>0</v>
-      </c>
       <c r="R155" t="n">
         <v>0</v>
       </c>
@@ -29157,9 +28944,6 @@
       <c r="O156" t="n">
         <v>5</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0.1061794304960066</v>
       </c>
@@ -29701,9 +29485,6 @@
       <c r="O159" t="n">
         <v>1</v>
       </c>
-      <c r="Q159" t="n">
-        <v>0</v>
-      </c>
       <c r="R159" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -30097,9 +29878,6 @@
       <c r="O161" t="n">
         <v>0</v>
       </c>
-      <c r="Q161" t="n">
-        <v>0</v>
-      </c>
       <c r="R161" t="n">
         <v>0</v>
       </c>
@@ -30245,9 +30023,6 @@
       <c r="O162" t="n">
         <v>3</v>
       </c>
-      <c r="Q162" t="n">
-        <v>0</v>
-      </c>
       <c r="R162" t="n">
         <v>0.06370765829760396</v>
       </c>
@@ -30789,9 +30564,6 @@
       <c r="O165" t="n">
         <v>1</v>
       </c>
-      <c r="Q165" t="n">
-        <v>0</v>
-      </c>
       <c r="R165" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -31185,9 +30957,6 @@
       <c r="O167" t="n">
         <v>0</v>
       </c>
-      <c r="Q167" t="n">
-        <v>0</v>
-      </c>
       <c r="R167" t="n">
         <v>0</v>
       </c>
@@ -31333,9 +31102,6 @@
       <c r="O168" t="n">
         <v>7</v>
       </c>
-      <c r="Q168" t="n">
-        <v>0</v>
-      </c>
       <c r="R168" t="n">
         <v>0.1486512026944092</v>
       </c>
@@ -31877,9 +31643,6 @@
       <c r="O171" t="n">
         <v>1</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -32273,9 +32036,6 @@
       <c r="O173" t="n">
         <v>0</v>
       </c>
-      <c r="Q173" t="n">
-        <v>0</v>
-      </c>
       <c r="R173" t="n">
         <v>0</v>
       </c>
@@ -32421,9 +32181,6 @@
       <c r="O174" t="n">
         <v>0</v>
       </c>
-      <c r="Q174" t="n">
-        <v>0</v>
-      </c>
       <c r="R174" t="n">
         <v>0</v>
       </c>
@@ -32965,9 +32722,6 @@
       <c r="O177" t="n">
         <v>14</v>
       </c>
-      <c r="Q177" t="n">
-        <v>0</v>
-      </c>
       <c r="R177" t="n">
         <v>0.2647148359429804</v>
       </c>
@@ -33361,9 +33115,6 @@
       <c r="O179" t="n">
         <v>0</v>
       </c>
-      <c r="Q179" t="n">
-        <v>0</v>
-      </c>
       <c r="R179" t="n">
         <v>0</v>
       </c>
@@ -33509,9 +33260,6 @@
       <c r="O180" t="n">
         <v>2</v>
       </c>
-      <c r="Q180" t="n">
-        <v>0</v>
-      </c>
       <c r="R180" t="n">
         <v>0.04247177219840264</v>
       </c>
@@ -34053,9 +33801,6 @@
       <c r="O183" t="n">
         <v>228</v>
       </c>
-      <c r="Q183" t="n">
-        <v>0</v>
-      </c>
       <c r="R183" t="n">
         <v>4.311070185357109</v>
       </c>
@@ -34449,9 +34194,6 @@
       <c r="O185" t="n">
         <v>0</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0</v>
       </c>
@@ -34597,9 +34339,6 @@
       <c r="O186" t="n">
         <v>0</v>
       </c>
-      <c r="Q186" t="n">
-        <v>0</v>
-      </c>
       <c r="R186" t="n">
         <v>0</v>
       </c>
@@ -35141,9 +34880,6 @@
       <c r="O189" t="n">
         <v>132</v>
       </c>
-      <c r="Q189" t="n">
-        <v>0</v>
-      </c>
       <c r="R189" t="n">
         <v>2.495882738890958</v>
       </c>
@@ -35537,9 +35273,6 @@
       <c r="O191" t="n">
         <v>0</v>
       </c>
-      <c r="Q191" t="n">
-        <v>0</v>
-      </c>
       <c r="R191" t="n">
         <v>0</v>
       </c>
@@ -35685,9 +35418,6 @@
       <c r="O192" t="n">
         <v>4</v>
       </c>
-      <c r="Q192" t="n">
-        <v>0</v>
-      </c>
       <c r="R192" t="n">
         <v>0.08494354439680528</v>
       </c>
@@ -36229,9 +35959,6 @@
       <c r="O195" t="n">
         <v>15</v>
       </c>
-      <c r="Q195" t="n">
-        <v>0</v>
-      </c>
       <c r="R195" t="n">
         <v>0.2836230385103362</v>
       </c>
@@ -36625,9 +36352,6 @@
       <c r="O197" t="n">
         <v>0</v>
       </c>
-      <c r="Q197" t="n">
-        <v>0</v>
-      </c>
       <c r="R197" t="n">
         <v>0</v>
       </c>
@@ -36773,9 +36497,6 @@
       <c r="O198" t="n">
         <v>8</v>
       </c>
-      <c r="Q198" t="n">
-        <v>0</v>
-      </c>
       <c r="R198" t="n">
         <v>0.1698870887936106</v>
       </c>
@@ -37317,9 +37038,6 @@
       <c r="O201" t="n">
         <v>8</v>
       </c>
-      <c r="Q201" t="n">
-        <v>0</v>
-      </c>
       <c r="R201" t="n">
         <v>0.151265620538846</v>
       </c>
@@ -37713,9 +37431,6 @@
       <c r="O203" t="n">
         <v>0</v>
       </c>
-      <c r="Q203" t="n">
-        <v>0</v>
-      </c>
       <c r="R203" t="n">
         <v>0</v>
       </c>
@@ -37861,9 +37576,6 @@
       <c r="O204" t="n">
         <v>10</v>
       </c>
-      <c r="Q204" t="n">
-        <v>0</v>
-      </c>
       <c r="R204" t="n">
         <v>0.2123588609920132</v>
       </c>
@@ -38405,9 +38117,6 @@
       <c r="O207" t="n">
         <v>2</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -38801,9 +38510,6 @@
       <c r="O209" t="n">
         <v>0</v>
       </c>
-      <c r="Q209" t="n">
-        <v>0</v>
-      </c>
       <c r="R209" t="n">
         <v>0</v>
       </c>
@@ -38949,9 +38655,6 @@
       <c r="O210" t="n">
         <v>4</v>
       </c>
-      <c r="Q210" t="n">
-        <v>0</v>
-      </c>
       <c r="R210" t="n">
         <v>0.08494354439680528</v>
       </c>
@@ -39493,9 +39196,6 @@
       <c r="O213" t="n">
         <v>1</v>
       </c>
-      <c r="Q213" t="n">
-        <v>0</v>
-      </c>
       <c r="R213" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -39889,9 +39589,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -40285,9 +39982,6 @@
       <c r="O217" t="n">
         <v>0</v>
       </c>
-      <c r="Q217" t="n">
-        <v>0</v>
-      </c>
       <c r="R217" t="n">
         <v>0</v>
       </c>
@@ -40433,9 +40127,6 @@
       <c r="O218" t="n">
         <v>9</v>
       </c>
-      <c r="Q218" t="n">
-        <v>0</v>
-      </c>
       <c r="R218" t="n">
         <v>0.1887543908990183</v>
       </c>
@@ -40977,9 +40668,6 @@
       <c r="O221" t="n">
         <v>0</v>
       </c>
-      <c r="Q221" t="n">
-        <v>0</v>
-      </c>
       <c r="R221" t="n">
         <v>0</v>
       </c>
@@ -41373,9 +41061,6 @@
       <c r="O223" t="n">
         <v>0</v>
       </c>
-      <c r="Q223" t="n">
-        <v>0</v>
-      </c>
       <c r="R223" t="n">
         <v>0</v>
       </c>
@@ -41521,9 +41206,6 @@
       <c r="O224" t="n">
         <v>13</v>
       </c>
-      <c r="Q224" t="n">
-        <v>0</v>
-      </c>
       <c r="R224" t="n">
         <v>0.272645231298582</v>
       </c>
@@ -42065,9 +41747,6 @@
       <c r="O227" t="n">
         <v>0</v>
       </c>
-      <c r="Q227" t="n">
-        <v>0</v>
-      </c>
       <c r="R227" t="n">
         <v>0</v>
       </c>
@@ -42461,9 +42140,6 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
@@ -42609,9 +42285,6 @@
       <c r="O230" t="n">
         <v>15</v>
       </c>
-      <c r="Q230" t="n">
-        <v>0</v>
-      </c>
       <c r="R230" t="n">
         <v>0.3145906514983638</v>
       </c>
@@ -43153,9 +42826,6 @@
       <c r="O233" t="n">
         <v>1</v>
       </c>
-      <c r="Q233" t="n">
-        <v>0</v>
-      </c>
       <c r="R233" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -43549,9 +43219,6 @@
       <c r="O235" t="n">
         <v>0</v>
       </c>
-      <c r="Q235" t="n">
-        <v>0</v>
-      </c>
       <c r="R235" t="n">
         <v>0</v>
       </c>
@@ -43697,9 +43364,6 @@
       <c r="O236" t="n">
         <v>2</v>
       </c>
-      <c r="Q236" t="n">
-        <v>0</v>
-      </c>
       <c r="R236" t="n">
         <v>0.04194542019978184</v>
       </c>
@@ -44241,9 +43905,6 @@
       <c r="O239" t="n">
         <v>0</v>
       </c>
-      <c r="Q239" t="n">
-        <v>0</v>
-      </c>
       <c r="R239" t="n">
         <v>0</v>
       </c>
@@ -44637,9 +44298,6 @@
       <c r="O241" t="n">
         <v>0</v>
       </c>
-      <c r="Q241" t="n">
-        <v>0</v>
-      </c>
       <c r="R241" t="n">
         <v>0</v>
       </c>
@@ -44785,9 +44443,6 @@
       <c r="O242" t="n">
         <v>1</v>
       </c>
-      <c r="Q242" t="n">
-        <v>0</v>
-      </c>
       <c r="R242" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -45329,9 +44984,6 @@
       <c r="O245" t="n">
         <v>1</v>
       </c>
-      <c r="Q245" t="n">
-        <v>0</v>
-      </c>
       <c r="R245" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -45725,9 +45377,6 @@
       <c r="O247" t="n">
         <v>0</v>
       </c>
-      <c r="Q247" t="n">
-        <v>0</v>
-      </c>
       <c r="R247" t="n">
         <v>0</v>
       </c>
@@ -45873,9 +45522,6 @@
       <c r="O248" t="n">
         <v>0</v>
       </c>
-      <c r="Q248" t="n">
-        <v>0</v>
-      </c>
       <c r="R248" t="n">
         <v>0</v>
       </c>
@@ -46417,9 +46063,6 @@
       <c r="O251" t="n">
         <v>1</v>
       </c>
-      <c r="Q251" t="n">
-        <v>0</v>
-      </c>
       <c r="R251" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -46813,9 +46456,6 @@
       <c r="O253" t="n">
         <v>0</v>
       </c>
-      <c r="Q253" t="n">
-        <v>0</v>
-      </c>
       <c r="R253" t="n">
         <v>0</v>
       </c>
@@ -46961,9 +46601,6 @@
       <c r="O254" t="n">
         <v>1</v>
       </c>
-      <c r="Q254" t="n">
-        <v>0</v>
-      </c>
       <c r="R254" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -47505,9 +47142,6 @@
       <c r="O257" t="n">
         <v>24</v>
       </c>
-      <c r="Q257" t="n">
-        <v>0</v>
-      </c>
       <c r="R257" t="n">
         <v>0.4516901398112726</v>
       </c>
@@ -47901,9 +47535,6 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -48049,9 +47680,6 @@
       <c r="O260" t="n">
         <v>5</v>
       </c>
-      <c r="Q260" t="n">
-        <v>0</v>
-      </c>
       <c r="R260" t="n">
         <v>0.1048635504994546</v>
       </c>
@@ -48593,9 +48221,6 @@
       <c r="O263" t="n">
         <v>37</v>
       </c>
-      <c r="Q263" t="n">
-        <v>0</v>
-      </c>
       <c r="R263" t="n">
         <v>0.6963556322090453</v>
       </c>
@@ -48989,9 +48614,6 @@
       <c r="O265" t="n">
         <v>0</v>
       </c>
-      <c r="Q265" t="n">
-        <v>0</v>
-      </c>
       <c r="R265" t="n">
         <v>0</v>
       </c>
@@ -49137,9 +48759,6 @@
       <c r="O266" t="n">
         <v>10</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.2097271009989092</v>
       </c>
@@ -49681,9 +49300,6 @@
       <c r="O269" t="n">
         <v>28</v>
       </c>
-      <c r="Q269" t="n">
-        <v>0</v>
-      </c>
       <c r="R269" t="n">
         <v>0.5269718297798179</v>
       </c>
@@ -50077,9 +49693,6 @@
       <c r="O271" t="n">
         <v>0</v>
       </c>
-      <c r="Q271" t="n">
-        <v>0</v>
-      </c>
       <c r="R271" t="n">
         <v>0</v>
       </c>
@@ -50225,9 +49838,6 @@
       <c r="O272" t="n">
         <v>4</v>
       </c>
-      <c r="Q272" t="n">
-        <v>0</v>
-      </c>
       <c r="R272" t="n">
         <v>0.08389084039956368</v>
       </c>
@@ -50769,9 +50379,6 @@
       <c r="O275" t="n">
         <v>15</v>
       </c>
-      <c r="Q275" t="n">
-        <v>0</v>
-      </c>
       <c r="R275" t="n">
         <v>0.2823063373820454</v>
       </c>
@@ -51165,9 +50772,6 @@
       <c r="O277" t="n">
         <v>0</v>
       </c>
-      <c r="Q277" t="n">
-        <v>0</v>
-      </c>
       <c r="R277" t="n">
         <v>0</v>
       </c>
@@ -51313,9 +50917,6 @@
       <c r="O278" t="n">
         <v>5</v>
       </c>
-      <c r="Q278" t="n">
-        <v>0</v>
-      </c>
       <c r="R278" t="n">
         <v>0.1048635504994546</v>
       </c>
@@ -51857,9 +51458,6 @@
       <c r="O281" t="n">
         <v>8</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0.1505633799370908</v>
       </c>
@@ -52253,9 +51851,6 @@
       <c r="O283" t="n">
         <v>0</v>
       </c>
-      <c r="Q283" t="n">
-        <v>0</v>
-      </c>
       <c r="R283" t="n">
         <v>0</v>
       </c>
@@ -52401,9 +51996,6 @@
       <c r="O284" t="n">
         <v>1</v>
       </c>
-      <c r="Q284" t="n">
-        <v>0</v>
-      </c>
       <c r="R284" t="n">
         <v>0.02097271009989092</v>
       </c>
@@ -52945,9 +52537,6 @@
       <c r="O287" t="n">
         <v>4</v>
       </c>
-      <c r="Q287" t="n">
-        <v>0</v>
-      </c>
       <c r="R287" t="n">
         <v>0.07492241081962027</v>
       </c>
@@ -53341,9 +52930,6 @@
       <c r="O289" t="n">
         <v>0</v>
       </c>
-      <c r="Q289" t="n">
-        <v>0</v>
-      </c>
       <c r="R289" t="n">
         <v>0</v>
       </c>
@@ -53737,9 +53323,6 @@
       <c r="O291" t="n">
         <v>0</v>
       </c>
-      <c r="Q291" t="n">
-        <v>0</v>
-      </c>
       <c r="R291" t="n">
         <v>0</v>
       </c>
@@ -53885,9 +53468,6 @@
       <c r="O292" t="n">
         <v>0</v>
       </c>
-      <c r="Q292" t="n">
-        <v>0</v>
-      </c>
       <c r="R292" t="n">
         <v>0</v>
       </c>
@@ -54429,9 +54009,6 @@
       <c r="O295" t="n">
         <v>5</v>
       </c>
-      <c r="Q295" t="n">
-        <v>0</v>
-      </c>
       <c r="R295" t="n">
         <v>0.09365301352452535</v>
       </c>
@@ -54825,9 +54402,6 @@
       <c r="O297" t="n">
         <v>0</v>
       </c>
-      <c r="Q297" t="n">
-        <v>0</v>
-      </c>
       <c r="R297" t="n">
         <v>0</v>
       </c>
@@ -54973,9 +54547,6 @@
       <c r="O298" t="n">
         <v>1</v>
       </c>
-      <c r="Q298" t="n">
-        <v>0</v>
-      </c>
       <c r="R298" t="n">
         <v>0.0207098401252117</v>
       </c>
@@ -55517,9 +55088,6 @@
       <c r="O301" t="n">
         <v>7</v>
       </c>
-      <c r="Q301" t="n">
-        <v>0</v>
-      </c>
       <c r="R301" t="n">
         <v>0.1311142189343355</v>
       </c>
@@ -55913,9 +55481,6 @@
       <c r="O303" t="n">
         <v>0</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0</v>
       </c>
@@ -56061,9 +55626,6 @@
       <c r="O304" t="n">
         <v>0</v>
       </c>
-      <c r="Q304" t="n">
-        <v>0</v>
-      </c>
       <c r="R304" t="n">
         <v>0</v>
       </c>
@@ -56605,9 +56167,6 @@
       <c r="O307" t="n">
         <v>3</v>
       </c>
-      <c r="Q307" t="n">
-        <v>0</v>
-      </c>
       <c r="R307" t="n">
         <v>0.0561918081147152</v>
       </c>
@@ -57001,9 +56560,6 @@
       <c r="O309" t="n">
         <v>0</v>
       </c>
-      <c r="Q309" t="n">
-        <v>0</v>
-      </c>
       <c r="R309" t="n">
         <v>0</v>
       </c>
@@ -57149,9 +56705,6 @@
       <c r="O310" t="n">
         <v>0</v>
       </c>
-      <c r="Q310" t="n">
-        <v>0</v>
-      </c>
       <c r="R310" t="n">
         <v>0</v>
       </c>
@@ -57693,9 +57246,6 @@
       <c r="O313" t="n">
         <v>3</v>
       </c>
-      <c r="Q313" t="n">
-        <v>0</v>
-      </c>
       <c r="R313" t="n">
         <v>0.0561918081147152</v>
       </c>
@@ -58089,9 +57639,6 @@
       <c r="O315" t="n">
         <v>0</v>
       </c>
-      <c r="Q315" t="n">
-        <v>0</v>
-      </c>
       <c r="R315" t="n">
         <v>0</v>
       </c>
@@ -58237,9 +57784,6 @@
       <c r="O316" t="n">
         <v>0</v>
       </c>
-      <c r="Q316" t="n">
-        <v>0</v>
-      </c>
       <c r="R316" t="n">
         <v>0</v>
       </c>
@@ -58781,9 +58325,6 @@
       <c r="O319" t="n">
         <v>10</v>
       </c>
-      <c r="Q319" t="n">
-        <v>0</v>
-      </c>
       <c r="R319" t="n">
         <v>0.1873060270490507</v>
       </c>
@@ -59177,9 +58718,6 @@
       <c r="O321" t="n">
         <v>0</v>
       </c>
-      <c r="Q321" t="n">
-        <v>0</v>
-      </c>
       <c r="R321" t="n">
         <v>0</v>
       </c>
@@ -59325,9 +58863,6 @@
       <c r="O322" t="n">
         <v>0</v>
       </c>
-      <c r="Q322" t="n">
-        <v>0</v>
-      </c>
       <c r="R322" t="n">
         <v>0</v>
       </c>
@@ -59869,9 +59404,6 @@
       <c r="O325" t="n">
         <v>59</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>1.105105559589399</v>
       </c>
@@ -60265,9 +59797,6 @@
       <c r="O327" t="n">
         <v>0</v>
       </c>
-      <c r="Q327" t="n">
-        <v>0</v>
-      </c>
       <c r="R327" t="n">
         <v>0</v>
       </c>
@@ -60413,9 +59942,6 @@
       <c r="O328" t="n">
         <v>2</v>
       </c>
-      <c r="Q328" t="n">
-        <v>0</v>
-      </c>
       <c r="R328" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -60957,9 +60483,6 @@
       <c r="O331" t="n">
         <v>174</v>
       </c>
-      <c r="Q331" t="n">
-        <v>0</v>
-      </c>
       <c r="R331" t="n">
         <v>3.259124870653482</v>
       </c>
@@ -61353,9 +60876,6 @@
       <c r="O333" t="n">
         <v>0</v>
       </c>
-      <c r="Q333" t="n">
-        <v>0</v>
-      </c>
       <c r="R333" t="n">
         <v>0</v>
       </c>
@@ -61501,9 +61021,6 @@
       <c r="O334" t="n">
         <v>3</v>
       </c>
-      <c r="Q334" t="n">
-        <v>0</v>
-      </c>
       <c r="R334" t="n">
         <v>0.06212952037563508</v>
       </c>
@@ -62045,9 +61562,6 @@
       <c r="O337" t="n">
         <v>108</v>
       </c>
-      <c r="Q337" t="n">
-        <v>0</v>
-      </c>
       <c r="R337" t="n">
         <v>2.022905092129747</v>
       </c>
@@ -62441,9 +61955,6 @@
       <c r="O339" t="n">
         <v>0</v>
       </c>
-      <c r="Q339" t="n">
-        <v>0</v>
-      </c>
       <c r="R339" t="n">
         <v>0</v>
       </c>
@@ -62589,9 +62100,6 @@
       <c r="O340" t="n">
         <v>2</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -63133,9 +62641,6 @@
       <c r="O343" t="n">
         <v>26</v>
       </c>
-      <c r="Q343" t="n">
-        <v>0</v>
-      </c>
       <c r="R343" t="n">
         <v>0.4869956703275317</v>
       </c>
@@ -63529,9 +63034,6 @@
       <c r="O345" t="n">
         <v>0</v>
       </c>
-      <c r="Q345" t="n">
-        <v>0</v>
-      </c>
       <c r="R345" t="n">
         <v>0</v>
       </c>
@@ -63677,9 +63179,6 @@
       <c r="O346" t="n">
         <v>2</v>
       </c>
-      <c r="Q346" t="n">
-        <v>0</v>
-      </c>
       <c r="R346" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -64221,9 +63720,6 @@
       <c r="O349" t="n">
         <v>6</v>
       </c>
-      <c r="Q349" t="n">
-        <v>0</v>
-      </c>
       <c r="R349" t="n">
         <v>0.1123836162294304</v>
       </c>
@@ -64617,9 +64113,6 @@
       <c r="O351" t="n">
         <v>0</v>
       </c>
-      <c r="Q351" t="n">
-        <v>0</v>
-      </c>
       <c r="R351" t="n">
         <v>0</v>
       </c>
@@ -64765,9 +64258,6 @@
       <c r="O352" t="n">
         <v>2</v>
       </c>
-      <c r="Q352" t="n">
-        <v>0</v>
-      </c>
       <c r="R352" t="n">
         <v>0.04141968025042339</v>
       </c>
@@ -65309,9 +64799,6 @@
       <c r="O355" t="n">
         <v>0</v>
       </c>
-      <c r="Q355" t="n">
-        <v>0</v>
-      </c>
       <c r="R355" t="n">
         <v>0</v>
       </c>
@@ -65705,9 +65192,6 @@
       <c r="O357" t="n">
         <v>0</v>
       </c>
-      <c r="Q357" t="n">
-        <v>0</v>
-      </c>
       <c r="R357" t="n">
         <v>0</v>
       </c>
@@ -65852,9 +65336,6 @@
       </c>
       <c r="O358" t="n">
         <v>1</v>
-      </c>
-      <c r="Q358" t="n">
-        <v>0</v>
       </c>
       <c r="R358" t="n">
         <v>0.0207098401252117</v>
